--- a/www/download/COUNTRY.ROU.EXI382.xlsx
+++ b/www/download/COUNTRY.ROU.EXI382.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>Romênia</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -967,2643 +972,4879 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.41111226993865</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.41111226993865</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.41111226993865</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.41111226993865</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.41111226993865</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.41111226993865</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.41111226993865</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.41111226993865</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.41111226993865</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.41111226993865</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.41111226993865</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.41111226993865</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.41111226993865</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.41111226993865</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.41111226993865</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.41111226993865</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.41172760736196</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.41172760736196</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.41172760736196</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.41172760736196</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.41172760736196</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.41172760736196</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.41172760736196</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.41172760736196</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.41172760736196</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.41172760736196</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.41172760736196</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>15.083</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>10.778</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>10.256</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>10.881</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>11.106</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>10.994</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>10.865</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>10.423</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>9.359</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>8.954</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>9.225</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>8.791</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>9.225</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>9.283</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>9.183</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>9.069</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>8.564</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>8.44</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>8.697</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>9.811</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>9.802</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>10.697</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>11.107</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>12.999</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>14.101</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>14.324</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>14.351</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>11.655</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>6.436</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>6.193</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>6.388</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>6.471</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>6.171</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>5.883</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>5.495</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>5.509</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>5.281</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>6.045</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>5.623</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>6.127</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>6.18</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>6.172</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>6.082</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>5.447</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>5.525</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>5.743</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>6.366</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>6.75</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>7.621</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>8.021</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>9.458</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>10.285</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>10.513</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>10.717</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>31377.358</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>20391.205</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>20364.145</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>23212.665</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>23250.058</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>22980.662</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>22829.129</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>21820.325</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>20110.784</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>19243.603</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>19788.84</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>18530.393</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>19331.072</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>19467.463</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>19125.764</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>18785.43</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>17620.586</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>17323.222</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>17795.596</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>20055.695</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>20156.896</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>22117.16</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>22979.544</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>27027.047</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>29355.007</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>29727.328</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>29871.476</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>24668.974</t>
+          <t>26455423816.8669</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>5835.129</t>
+          <t>25275299353.6718</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>5024.472</t>
+          <t>26332328382.8777</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>5729.654</t>
+          <t>30815774701.1297</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>5730.634</t>
+          <t>30296050797.673</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>4615.718</t>
+          <t>30514869770.4891</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3600.745</t>
+          <t>30011810296.7868</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2929.859</t>
+          <t>29261527808.7452</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>4680.224</t>
+          <t>25404490576.455</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>4496.728</t>
+          <t>25596809607.327</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>7033.792</t>
+          <t>25340851090.0758</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>6308.701</t>
+          <t>23161297713.2389</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>7504.368</t>
+          <t>23781742663.7589</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>7762.269</t>
+          <t>24824673936.7838</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>7860.876</t>
+          <t>22867472245.4795</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>7605.19</t>
+          <t>22964362181.087</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>5991.702</t>
+          <t>22925986318.3759</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>6595.933</t>
+          <t>23778840672.3513</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>6970.37</t>
+          <t>22451702052.6884</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>13761.899</t>
+          <t>24448710240.5601</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>14520.096</t>
+          <t>23073622393.0735</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>16370.961</t>
+          <t>25521750180.5395</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>17160.714</t>
+          <t>24803828411.3869</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>20311.628</t>
+          <t>27102344899.986</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>22092.111</t>
+          <t>29379854145.1796</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>22441.775</t>
+          <t>32409823419.4005</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>22894.987</t>
+          <t>30663161852.6597</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>5527257220.39992</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>5265103592.53946</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>5982190373.78242</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>6463578405.47668</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>6432870433.51661</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>7244107961.98313</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>6642724227.81895</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>6772214889.78463</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>5777618218.24519</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>5332723682.70312</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>5706317356.87952</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>5491950987.28586</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>5841193137.53389</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>6391718774.5562</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>5115192774.09916</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>5024157394.99339</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>4443275386.80377</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>4980309920.04942</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>4402553817.14132</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>4582424198.75689</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>4128052655.61438</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>3895365505.22111</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>4991488844.61485</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>5447929140.61737</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>5301752886.98409</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>6834713826.24598</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>6045419114.5706</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>167671875.897439</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>303661904.892517</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>49968733.7782011</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>68287325.3178587</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>77275720.6097502</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>167225204.487007</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>50818922.8336711</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>40945555.0615343</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>37779929.4507758</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>31210618.0315869</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>27051753.8725476</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>20155372.200757</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>16654681.6951238</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>18978724.0164919</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>13797331.6753668</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>13917785.8996051</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>13873194.3610255</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>13697260.6052546</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>11944677.4041858</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>360432540.354758</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>333293249.638308</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>364596774.727035</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>314390686.427555</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>349027043.455203</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>329430495.833413</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>353794164.813589</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>350316028.295831</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>72149.8915877251</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>124635.882491591</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>133387.098989124</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>161090.326914908</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>169572.677839713</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>201482.932719992</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>202469.630413696</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>183358.425537321</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>152293.896737878</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>141894.248005507</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>152197.301403947</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>149176.12708094</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>160852.390710852</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>161127.173200392</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>156626.140504067</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>175038.655063738</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>180340.870729082</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>192846.216210231</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>179001.365839061</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>217051.162998134</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>237837.211212679</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>230300.201977265</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>245052.26842542</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>259360.242088139</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>299565.09433983</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>318423.890289232</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>303200.677114002</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>98615.3077027208</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>192068.830469068</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>217942.781565979</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>262209.609444666</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>271915.988593574</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>327388.345813727</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>323309.773853573</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>305567.504476426</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>243699.728520902</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>239955.289698612</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>254669.770079921</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>248991.128135887</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>264878.960546397</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>277825.574909791</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>256462.110822277</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>297006.357195205</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>308682.6044826</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>353385.65279703</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>325930.892799823</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>367372.159354783</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>391655.061527525</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>394858.169710743</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>405718.469765676</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>431156.425999533</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>497984.730014021</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>522590.804728939</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>485418.094756605</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>3.46314932633971</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>0.108264803802019</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>-0.16009493412126</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>-0.11354769129973</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-0.109163777007543</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-0.362831417722494</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>-0.4579415196977</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>-0.567370639046447</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>-0.18993886006093</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>-0.156767110474281</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>0.232632459799355</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>0.148717644167247</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>0.284732044175337</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>0.214425927324787</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>0.536770234704125</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>0.51372447200436</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>0.348487653451445</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>0.324402116713282</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>0.58325605762373</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>2.00319192144493</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>2.51742017598456</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>3.20267658267904</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2.43799501696369</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>2.72832097564416</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>3.16694461973609</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>2.28349889570746</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>2.78716294842687</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>474.227977288948</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>818.108922501331</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>965.975613005645</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>1011.91051357707</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>994.169077599741</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>1173.93335742307</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1129.10052825382</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>1232.43219104259</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>1048.83604150702</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>1009.75605595355</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>943.973094603729</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>976.624637636517</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>953.415130338825</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>1034.32564802857</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>828.827657998225</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>826.069943274369</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>815.713937104877</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>901.462508380177</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>766.568083497157</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>719.771392529332</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>611.555820962247</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>511.150901298579</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>622.340582492162</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>576.019773152372</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>515.50088554422</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>650.146890688502</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>564.096135876951</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>-3176340153.68926</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>-2071486411.12445</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>-1224890191.54888</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>-2265515713.27927</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>-2917044214.75071</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>-3077812108.92626</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>-2816188259.29556</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>-1944151527.36387</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>-1891176034.78396</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>-1280103386.93297</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>-1244825524.04369</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>-726337833.761013</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>-1292574617.65763</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>-983486473.824765</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>-162069023.31807</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>281469675.720996</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>205136405.332563</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>5944773.33268777</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>612980592.971685</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>-715086000.220121</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>0.057</t>
+          <t>-843564865.706806</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>-371710109.451001</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>0.074</t>
+          <t>-466560499.967107</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>-684986622.667326</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>-805700224.376437</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>0.086</t>
+          <t>-638294854.366433</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>-1957415200.56051</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>-2951308947.64637</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>-1887217444.59404</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>-1061019550.83749</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>-2098677771.8309</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-2752846864.8846</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-2924544471.44023</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>-2656479436.01909</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>-1803647831.40032</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>-1783696282.92527</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>-967804377.957393</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>-981332836.101952</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>-462794995.03621</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>-1028584320.30045</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>-619797444.704917</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>281794252.454822</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>661475174.965196</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>637811351.051159</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>425507599.202156</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>986092063.264253</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>-407815821.260384</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>-577926965.894449</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>-91062862.3047877</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>-170446750.742665</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>-364489776.122082</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>-479471717.68135</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>-268479355.131116</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>-63489854.4819191</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>-225031206.042882</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>-184268966.530414</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>-163870640.711389</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>-166837941.448365</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-164197349.866102</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-153267637.486033</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>-159708823.27647</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>-140503695.963553</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>-107479751.858688</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>-312299008.975578</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>-263492687.941735</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>-263542838.724802</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>-263990297.357181</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>-363689029.119848</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>-443863275.772891</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>-380005499.244201</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>-432674945.718596</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>-419562825.869468</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>-373111470.292567</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>-307270178.959737</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>-265637899.812357</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>-280647247.146214</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>-296113749.224442</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>-320496846.545244</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>-326228506.695087</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>-369815499.235317</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>-1893925346.07859</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>2116.55027736861</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.057</t>
+          <t>906.681324484619</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>811.327810878762</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>897.010410958468</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>885.641826104849</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>747.993453037528</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.085</t>
+          <t>612.038516453792</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.092</t>
+          <t>533.186351229342</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.099</t>
+          <t>849.621319392358</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.116</t>
+          <t>851.459516777809</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.146</t>
+          <t>1163.5718775858</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.179</t>
+          <t>1121.86595298151</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.234</t>
+          <t>1224.88296934789</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.259</t>
+          <t>1256.11188426291</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.235</t>
+          <t>1273.7176745112</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>0.229</t>
+          <t>1250.44228872167</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>1099.9801729342</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>1193.89885423637</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>0.255</t>
+          <t>1213.67356177789</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>0.263</t>
+          <t>2161.61163133126</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>0.285</t>
+          <t>2151.09878339341</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>0.297</t>
+          <t>2148.20192310282</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>0.326</t>
+          <t>2139.60382146233</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>0.356</t>
+          <t>2147.58660262978</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>0.396</t>
+          <t>2148.06364148768</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>0.392</t>
+          <t>2134.75659762334</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>0.399</t>
+          <t>2136.32398514396</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>2080.35703132009</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>1891.9284653916</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>1985.58356084214</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>2133.34053249296</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>2093.54361763348</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>2090.36730461359</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>2101.20103453352</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>2093.55870895927</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>2148.74873120861</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>2149.16272057189</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>2145.20146996652</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>2107.95420159937</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>2095.48644459131</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>2097.17679123534</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>2082.75860567031</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>2071.29799104696</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>2057.54224126851</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>2052.44150089437</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>2046.15285554977</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>2044.21146413859</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>0.057</t>
+          <t>2056.44077809618</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>2067.63975022321</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>0.074</t>
+          <t>2068.86150343504</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>2079.15013343483</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>2081.72668391395</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>0.086</t>
+          <t>2075.33376174511</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>2081.463526111</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>7860.88998353154</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>8765.80361487018</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>9890.50461538196</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>9210.92043993893</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>10475.1527774021</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>15128.538096494</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>16977.5293546267</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>19542.4885180179</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>20008.9301798187</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>23320.1359703376</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>19075.7256684874</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>22539.2364236823</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>30605.5879964658</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>36936.1174003222</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>34097.2605830879</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>43159.758597873</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>51382.1680895412</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>54001.7228917429</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>63245.5732922732</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>68142.7194725878</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>74400.862751887</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>79725.5126665852</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>87652.9923586862</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>95290.7001760949</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>101900.082353369</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>101898.878567191</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>100219.099265928</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>3580622958.0331</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2854890297.98079</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>3097209012.77188</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>3813827247.69205</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>4749079229.53365</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>5552180613.89292</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>5318246262.6836</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>4828032121.55634</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>4511477393.48108</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>4274555045.89223</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>3347180399.30666</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>2821745299.55041</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>3032007645.44552</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>3074840268.1392</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>3240564705.77361</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>3580616716.23762</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>4093524265.96169</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>4485823109.07799</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>4669231762.97254</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>5828140364.61195</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>6124904472.99947</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>6692465626.72653</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>6534906882.44196</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>7610408285.82971</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>8062674569.78897</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>8262842519.12991</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>8104169491.93242</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>9744.05805944645</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>11757.8801517149</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>12685.2995987019</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>13009.2226687115</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>12480.7263664511</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>17928.873330988</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>21486.5303744995</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>23119.471840582</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>25149.9924424684</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>30484.9658690835</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>29727.1433932769</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>37972.6271537095</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>54072.4812210361</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>61454.4743962224</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>44588.204137789</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>53718.8138573635</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>61394.0640201321</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>62933.1338980103</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>64708.9700559694</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>69007.1489199397</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>75704.2164703135</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>81789.8197298173</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>92859.0218037083</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>103319.993186973</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>113170.587684124</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>113169.384098849</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>111489.604740338</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>31377.358</t>
+          <t>1471146933.11197</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>20391.205</t>
+          <t>1391208476.46181</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>20364.145</t>
+          <t>2395470114.1553</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>23212.665</t>
+          <t>2263905295.16562</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>23250.058</t>
+          <t>2199945241.36782</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>22980.662</t>
+          <t>2908814132.90668</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>22829.129</t>
+          <t>3229265127.28076</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>21820.325</t>
+          <t>3482429914.5237</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>20110.784</t>
+          <t>3493652970.84785</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>19243.603</t>
+          <t>4308408679.53717</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>19788.84</t>
+          <t>3883810713.53545</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>18530.393</t>
+          <t>4391767903.00994</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>19331.072</t>
+          <t>4653608243.24995</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>19467.463</t>
+          <t>5451333486.54572</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>19125.764</t>
+          <t>4622672456.33831</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>18785.43</t>
+          <t>5164039196.57179</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>17620.586</t>
+          <t>5453190012.58522</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>17323.222</t>
+          <t>5465570623.85814</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>17795.596</t>
+          <t>5449849660.24704</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>20055.695</t>
+          <t>5204948481.21767</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>20156.896</t>
+          <t>5407328142.51622</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>22117.16</t>
+          <t>6539688764.8504</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>22979.544</t>
+          <t>6569805491.76264</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>27027.047</t>
+          <t>7723450736.14513</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>29355.007</t>
+          <t>8285604132.35939</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>29727.328</t>
+          <t>8718252471.06034</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>29871.476</t>
+          <t>7244896826.12976</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>24668.974</t>
+          <t>-1883.16807591491</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>5835.129</t>
+          <t>-2992.07653684467</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>5024.472</t>
+          <t>-2794.79498331995</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>5729.654</t>
+          <t>-3798.30222877255</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>5730.634</t>
+          <t>-2005.57358904903</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>4615.718</t>
+          <t>-2800.33523449396</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>3600.745</t>
+          <t>-4509.00101987284</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2929.859</t>
+          <t>-3576.98332256404</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>4680.224</t>
+          <t>-5141.06226264967</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>4496.728</t>
+          <t>-7164.82989874588</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>7033.792</t>
+          <t>-10651.4177247895</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>6308.701</t>
+          <t>-15433.3907300272</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>7504.368</t>
+          <t>-23466.8932245703</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>7762.269</t>
+          <t>-24518.3569959002</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>7860.876</t>
+          <t>-10490.9435547011</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>7605.19</t>
+          <t>-10559.0552594904</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>5991.702</t>
+          <t>-10011.8959305909</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>6595.933</t>
+          <t>-8931.41100626732</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>6970.37</t>
+          <t>-1463.39676369621</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>13761.899</t>
+          <t>-864.429447351918</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>14520.096</t>
+          <t>-1303.35371842657</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>16370.961</t>
+          <t>-2064.30706323205</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>17160.714</t>
+          <t>-5206.02944502217</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>20311.628</t>
+          <t>-8029.29301087793</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>22092.111</t>
+          <t>-11270.5053307546</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>22441.775</t>
+          <t>-11270.5055316589</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>22894.987</t>
+          <t>-11270.5054744096</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>28870.013</t>
+          <t>2109476024.92113</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>27572.874</t>
+          <t>1463681821.51897</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>28322.976</t>
+          <t>701738898.616583</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>33356.996</t>
+          <t>1549921952.52644</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>32773.958</t>
+          <t>2549133988.16583</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>32968.439</t>
+          <t>2643366480.98624</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>32196.944</t>
+          <t>2088981135.40284</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>31326.822</t>
+          <t>1345602207.03264</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>27233.566</t>
+          <t>1017824422.63323</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>27325.576</t>
+          <t>-33853633.6449401</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>26999.045</t>
+          <t>-536630314.228797</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>24705.083</t>
+          <t>-1570022603.45953</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>25380.827</t>
+          <t>-1621600597.80442</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>26512.848</t>
+          <t>-2376493218.40653</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>24427.004</t>
+          <t>-1382107750.56469</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>24347.085</t>
+          <t>-1583422480.33417</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>24166.378</t>
+          <t>-1359665746.62353</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>25149.882</t>
+          <t>-979747514.780156</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>23664.099</t>
+          <t>-780617897.274504</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>25893.363</t>
+          <t>623191883.394282</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>24342.015</t>
+          <t>717576330.483255</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>26891.336</t>
+          <t>152776861.876127</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>26282.873</t>
+          <t>-34898609.3206753</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>28476.196</t>
+          <t>-113042450.315425</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>30865.995</t>
+          <t>-222929562.570416</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>34179.586</t>
+          <t>-455409951.930432</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>32409.134</t>
+          <t>859272665.802662</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.094</t>
+          <t>14051.3492253003</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.179</t>
+          <t>13575.7974328625</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.201</t>
+          <t>15571.3838948588</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.246</t>
+          <t>18462.3231232255</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.255</t>
+          <t>17195.2726714385</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.307</t>
+          <t>20900.3615895855</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.301</t>
+          <t>22887.2878067359</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.285</t>
+          <t>24411.003473795</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.228</t>
+          <t>25461.464388012</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.224</t>
+          <t>28938.9910086473</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.237</t>
+          <t>36552.2869846481</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.232</t>
+          <t>43655.5468724449</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.246</t>
+          <t>61825.0333913931</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.261</t>
+          <t>72199.7553157083</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.239</t>
+          <t>58534.0250754505</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>0.274</t>
+          <t>53325.9086813774</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>0.284</t>
+          <t>57211.6200138173</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>0.326</t>
+          <t>50134.470750265</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>0.298</t>
+          <t>56177.4139496247</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>0.335</t>
+          <t>54752.9014401506</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>0.352</t>
+          <t>61457.0399021636</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>0.353</t>
+          <t>62290.6978629353</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>0.362</t>
+          <t>64047.8840044983</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>0.381</t>
+          <t>73155.9948584722</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>0.437</t>
+          <t>80966.2178393989</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>0.461</t>
+          <t>78859.4960348304</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>0.429</t>
+          <t>77897.5089782624</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>19355.575</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>16401.46</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>16116.124</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>18931.889</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>18893.271</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>18779.61</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>18794.607</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>17558.633</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>15875.885</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>15136.32</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>15144.354</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>13876.449</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>14441.88</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>14397.269</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>13965.587</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>13533.889</t>
-        </is>
-      </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>13393.992</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>12976.36</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>12330.483</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>14444.81</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>14011.733</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>14885.507</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>14981.409</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>16303.296</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>17673.592</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>19747.883</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>19152.75</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>16249.700326284</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.106</t>
+          <t>16529.846888785</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>18902.1053351338</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>23090.8321655679</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.147</t>
+          <t>21830.0218446614</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.175</t>
+          <t>27799.910999425</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.176</t>
+          <t>27587.3794478425</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>29742.2800634275</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>31364.6943887955</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.124</t>
+          <t>36498.2385472092</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>47017.7691076882</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>57423.3219926449</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>77731.7122107202</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.142</t>
+          <t>94693.9022288232</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>76711.6279323407</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>0.153</t>
+          <t>61933.0204006349</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>0.157</t>
+          <t>61722.0920368322</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>0.168</t>
+          <t>72039.6907232837</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>0.155</t>
+          <t>73639.3184069597</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>0.187</t>
+          <t>80496.4105629079</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>0.203</t>
+          <t>81919.8973525388</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>0.195</t>
+          <t>79543.4385381852</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>0.206</t>
+          <t>106492.444114882</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>0.218</t>
+          <t>120224.403629192</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>110735.193745144</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>0.266</t>
+          <t>124427.030587416</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>0.253</t>
+          <t>125497.724854007</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>5448.904</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>5166.819</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>5838.352</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>6307.181</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>6263.033</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>7010.56</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>6406.548</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>6553.192</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>5496.007</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>5119.607</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>5476.217</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>5244.851</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>5518.146</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>6068.277</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>4796.6</t>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>4709.416</t>
-        </is>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>4187.141</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>4662.913</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>4128.537</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>4259.768</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>3790.84</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>3585.29</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>4620.366</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>4964.842</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>4822.245</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>6216.183</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>5606.091</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>352.73</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>12.93</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>-13.94</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>-9.16</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>-8.5</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>-34.16</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>-43.8</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>-55.29</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>-14.84</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>-12.17</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>28.44</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>20.28</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>35.99</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>27.92</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>63.88</t>
-        </is>
-      </c>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>61.49</t>
-        </is>
-      </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>43.1</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>41.46</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>68.83</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>223.07</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>283.03</t>
-        </is>
-      </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>356.61</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>271.41</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>309.11</t>
-        </is>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>358.13</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>261.02</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>308.39</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>243.824</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>418.855</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>69.653</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>95.581</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>107.966</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>230.689</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>70.527</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>56.781</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>52.353</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>42.887</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>37.013</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>27.537</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>22.837</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>26.352</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>18.962</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>18.989</t>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>18.913</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>18.728</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>16.277</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>494.193</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>456.924</t>
-        </is>
-      </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>499.87</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>431.143</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>478.485</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>451.636</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>485.021</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>480.235</t>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>20820.4191703796</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>21216.0949439528</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>21866.6970906574</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>25655.1228079938</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>22513.6812236857</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>25589.7897321823</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>32604.4415299232</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>35641.0685574125</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>40172.1560343716</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>47214.4839120026</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>60470.0699705416</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>75087.8085004986</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>95892.9660908735</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>103920.480850542</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>94023.9377970043</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>108646.933775562</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>115791.361147685</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>109049.685160118</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>121479.504053794</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>124976.131001865</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>136350.40917557</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>149952.788847978</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>148025.057997919</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>158538.055262034</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>192459.739955104</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>179538.835279179</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>181002.627643041</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>24668974339.7342</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>5835128999.98306</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>5024471999.99089</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>5729654000.00001</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>5730633999.99378</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>4615718000.00198</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>3600744999.99881</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>2929859000.00766</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>4680224000.00444</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>4496728000.00799</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>7033792000.00615</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>6308700999.99699</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>7504368000.00686</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>7762268999.98967</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>7860876000.00922</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>7605190000.00318</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>5991701999.98958</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>6595933000.00161</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>6970370000.00348</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>13761899334.3404</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>14520095698.3847</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>16370961389.7685</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>17160713775.0157</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>20311628488.7868</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>22092110667.5886</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>22441775300.9552</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>22894987278.4134</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>31377358376.5468</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>20391204999.9925</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>20364144999.9962</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>23212665000.0018</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>23250057999.9947</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>22980661999.9986</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>22829128999.9985</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>21820325000.0014</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>20110784000.0013</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>19243603000.0036</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>19788840000.0002</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>18530392999.9988</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>19331072000.0008</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>19467462999.9979</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>19125764000.0052</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>18785430000</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>17620585999.9983</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>17323222000</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>17795596000.0016</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>20055694560.121</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>20156895944.0141</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>22117159789.654</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>22979544036.7834</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>27027047342.927</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>29355006682.1283</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>29727327535.6592</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>29871475574.8814</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>19355574755.6787</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>16401459999.9939</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>16116123999.9944</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>18931889000.0052</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>18893270999.993</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>18779609999.9995</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>18794606999.9988</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>17558633000.0021</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>15875884999.9998</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>15136320000.0037</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>15144353999.9995</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>13876448999.998</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>14441880000.0003</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>14397268999.9982</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>13965587000.0045</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>13533888999.9992</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>13393991999.9994</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>12976359999.9989</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>12330482999.9994</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>14444809864.8466</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>14011732622.9355</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>14885507435.9922</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>14981409205.639</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>16303295765.8486</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>17673591675.0768</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>19747882977.2855</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>19152750044.9779</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>15082679.5132547</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>10778000.0000009</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>10255999.9999996</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>10880899.9999996</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>11105600.0000021</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>10993599.9999994</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>10864799.9999993</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>10422600.0000012</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>9359300.00000028</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>8954000.00000134</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>9224700.00000002</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>8790699.99999965</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>9225100.00000072</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>9282699.99999887</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>9182899.99999773</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>9069399.99999934</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>8563899.99999944</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>8440300.0000006</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>8697099.99999987</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>9810968.63605167</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>9801836.33718596</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>10696814.9491547</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>11107338.0207565</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>12999084.0528083</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>14101277.9962721</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>14324118.8880684</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>14351188.5748453</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>11655274.4357218</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>6435699.99999712</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>6192899.99999975</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>6387500.00000312</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>6470599.99999972</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>6170799.99999733</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>5883199.99999651</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>5495000.00000455</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>5508599.99999964</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>5281200.0000012</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>6044999.99999998</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>5623400.00000068</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>6126600.00000005</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>6179599.99999889</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>6171599.99999676</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>6081999.99999841</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>5447099.99999975</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>5524700.00000162</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>5743200.00000059</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>6366499.48347335</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>6750083.17167046</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>7620774.01277184</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>8020509.9667877</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>9457885.63958941</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>10284663.0057424</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>10512568.6581505</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>10717001.4649583</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>31377358376.5468</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>20391204999.9925</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>20364144999.9962</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>23212665000.0018</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>23250057999.9947</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>22980661999.9986</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>22829128999.9985</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>21820325000.0014</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>20110784000.0013</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>19243603000.0036</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>19788840000.0002</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>18530392999.9988</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>19331072000.0008</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>19467462999.9979</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>19125764000.0052</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>18785430000</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>17620585999.9983</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>17323222000</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>17795596000.0016</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>20055694560.121</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>20156895944.0141</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>22117159789.654</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>22979544036.7834</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>27027047342.927</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>29355006682.1283</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>29727327535.6592</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>29871475574.8814</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>24668974339.7342</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>5835128999.98306</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>5024471999.99089</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>5729654000.00001</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>5730633999.99378</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>4615718000.00198</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>3600744999.99881</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>2929859000.00766</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>4680224000.00444</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>4496728000.00799</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>7033792000.00615</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>6308700999.99699</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>7504368000.00686</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>7762268999.98967</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>7860876000.00922</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>7605190000.00318</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>5991701999.98958</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>6595933000.00161</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>6970370000.00348</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>13761899334.3404</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>14520095698.3847</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>16370961389.7685</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>17160713775.0157</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>20311628488.7868</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>22092110667.5886</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>22441775300.9552</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>22894987278.4134</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>76395.7014494139</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>81260.7787728893</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>87443.9697625209</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>97449.3690261279</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>89757.6079678161</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>112778.49727224</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>120656.73424283</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>130950.971640606</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>140502.773009196</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>165330.827727063</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>208075.877375472</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>255844.832202755</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>334057.867343559</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>369310.984939556</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>335710.712285643</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>326633.264346995</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>341319.114225325</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>343143.551513439</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>364173.408794827</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>375775.650102517</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>407678.444781223</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>425600.907412109</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>465878.807689049</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>510228.491350337</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>567396.239923035</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>562115.452574153</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>572045.89346898</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>20220.556507372</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>20488.4538332231</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>23113.4277626922</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>27774.8024663788</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>26044.573337093</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>32495.5058142712</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>32350.0766284633</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>34180.2894367512</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>35527.6976515179</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>40350.6511769456</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>52987.305915443</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>64350.3802293215</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>87216.0485604221</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>105184.933716962</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>85209.3287090859</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>70982.5607918033</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>72404.8696595317</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>82456.7787147499</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>85015.3591092699</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>90925.2909363821</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>94326.4722246506</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>95184.8232756216</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>121742.874913064</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>136295.178491234</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>129763.60288743</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>142665.598910231</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>141201.769408935</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
         </is>
       </c>
     </row>
@@ -3614,7 +5855,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3637,36 +5878,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3678,331 +5934,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -4039,6 +6659,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>EXI382</t>
